--- a/product_order_forms/004_sock_order_form_template--product_order_forms.xlsx
+++ b/product_order_forms/004_sock_order_form_template--product_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -834,8 +834,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -863,12 +863,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'al'}</t>
+          <t>al</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'AL'}</t>
+          <t>AL</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'ak'}</t>
+          <t>ak</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'AK'}</t>
+          <t>AK</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'az'}</t>
+          <t>az</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'AZ'}</t>
+          <t>AZ</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'ar'}</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'AR'}</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Green'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
